--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
@@ -603,9 +603,7 @@
           <t>019B</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -751,9 +749,7 @@
           <t>043ABC</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1133,9 +1129,7 @@
           <t>098C</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>2</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1539,9 +1533,7 @@
           <t>150B</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>2</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
